--- a/JsonConverter/ExcelFiles/MGMonster.xlsx
+++ b/JsonConverter/ExcelFiles/MGMonster.xlsx
@@ -19,7 +19,73 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="27">
+  <x:si>
+    <x:t>녹색 고블린, 적을 보면 돌을 던진다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>빨간색 고블린, 근접 무기를 휘둘러 적을 공격한다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MoveSpeed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DetectRange</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PatrolRange</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AttackRange</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PrefabPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PatrolSpeed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>몬스터를 우선 프리팹으로 구현</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AttackCoolTime</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mob_goblin_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>몬스터 설명 (도감용)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mob_goblin_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>몬스터 표기용 Icon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AttackDamage</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MaxHp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
   <x:si>
     <x:t>레드 고블린</x:t>
   </x:si>
@@ -27,49 +93,13 @@
     <x:t>그린 고블린</x:t>
   </x:si>
   <x:si>
-    <x:t>mob_goblin_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mob_goblin_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>빨간색 고블린, 근접 무기를 휘둘러 적을 공격한다.</x:t>
-  </x:si>
-  <x:si>
     <x:t>Name</x:t>
   </x:si>
   <x:si>
     <x:t>(name)</x:t>
   </x:si>
   <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PrefabPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>몬스터를 우선 프리팹으로 구현</x:t>
-  </x:si>
-  <x:si>
-    <x:t>몬스터 표기용 Icon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>몬스터 설명 (도감용)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>녹색 고블린, 적을 보면 돌을 던진다.</x:t>
+    <x:t>float</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -216,57 +246,54 @@
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="17">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+  <x:cellXfs count="16">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -881,103 +908,182 @@
     <x:col min="4" max="4" width="20.26953125" style="3" customWidth="1"/>
     <x:col min="5" max="5" width="30.54296875" style="3" customWidth="1"/>
     <x:col min="6" max="6" width="26.54296875" style="3" customWidth="1"/>
-    <x:col min="7" max="16384" width="12.54296875" style="3"/>
+    <x:col min="7" max="13" width="20.71484375" style="3" customWidth="1"/>
+    <x:col min="14" max="16384" width="12.54296875" style="3"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="D1" s="2" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E1" s="2" t="s">
-        <x:v>13</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:6" ht="13.199999999999999">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:13" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="F2" s="1"/>
-    </x:row>
-    <x:row r="3" spans="1:6" s="13" customFormat="1" ht="15.75" customHeight="1">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F2" s="1" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G2" s="3" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H2" s="3" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="I2" s="3" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="J2" s="3" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="K2" s="3" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="L2" s="3" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="M2" s="3" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:13" s="13" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="12" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B3" s="12" t="s">
-        <x:v>5</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C3" s="12" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D3" s="14" t="s">
         <x:v>9</x:v>
-      </x:c>
-      <x:c r="D3" s="14" t="s">
-        <x:v>8</x:v>
       </x:c>
       <x:c r="E3" s="14" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="F3" s="15"/>
+      <x:c r="F3" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="G3" s="13" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="H3" s="13" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I3" s="13" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="J3" s="13" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K3" s="13" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="L3" s="13" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="M3" s="13" t="s">
+        <x:v>13</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A4" s="4" t="s">
-        <x:v>3</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B4" s="4" t="s">
-        <x:v>1</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C4" s="4" t="s">
-        <x:v>16</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D4" s="5"/>
       <x:c r="E4" s="5"/>
-      <x:c r="F4" s="16"/>
-      <x:c r="G4" s="5"/>
-      <x:c r="H4" s="5"/>
-      <x:c r="I4" s="5"/>
-      <x:c r="J4" s="5"/>
-      <x:c r="K4" s="5"/>
-      <x:c r="L4" s="5"/>
-      <x:c r="M4" s="5"/>
+      <x:c r="F4" s="15">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G4" s="5">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H4" s="5">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I4" s="5">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="J4" s="5">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K4" s="5">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L4" s="5">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M4" s="5">
+        <x:v>1.5</x:v>
+      </x:c>
       <x:c r="N4" s="5"/>
       <x:c r="O4" s="5"/>
     </x:row>
     <x:row r="5" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A5" s="4" t="s">
-        <x:v>2</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B5" s="6" t="s">
-        <x:v>0</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C5" s="6" t="s">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="5"/>
       <x:c r="E5" s="5"/>
-      <x:c r="F5" s="5"/>
-      <x:c r="G5" s="5"/>
-      <x:c r="H5" s="5"/>
-      <x:c r="I5" s="5"/>
-      <x:c r="J5" s="5"/>
-      <x:c r="K5" s="5"/>
-      <x:c r="L5" s="5"/>
-      <x:c r="M5" s="5"/>
+      <x:c r="F5" s="5">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="G5" s="5">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H5" s="5">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I5" s="5">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="J5" s="5">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K5" s="5">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L5" s="5">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M5" s="5">
+        <x:v>1.5</x:v>
+      </x:c>
       <x:c r="N5" s="5"/>
       <x:c r="O5" s="5"/>
     </x:row>

--- a/JsonConverter/ExcelFiles/MGMonster.xlsx
+++ b/JsonConverter/ExcelFiles/MGMonster.xlsx
@@ -19,87 +19,93 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="27">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="29">
+  <x:si>
+    <x:t>Prefab/2D/Monster</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefab/2D/Monster_Red</x:t>
+  </x:si>
+  <x:si>
+    <x:t>빨간색 고블린, 근접 무기를 휘둘러 적을 공격한다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>레드 고블린</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MaxHp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그린 고블린</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>float</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PrefabPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AttackRange</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PatrolRange</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DetectRange</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MoveSpeed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PatrolSpeed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>몬스터를 우선 프리팹으로 구현</x:t>
+  </x:si>
+  <x:si>
+    <x:t>몬스터 표기용 Icon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mob_goblin_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>몬스터 설명 (도감용)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AttackDamage</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mob_goblin_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AttackCoolTime</x:t>
+  </x:si>
   <x:si>
     <x:t>녹색 고블린, 적을 보면 돌을 던진다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>빨간색 고블린, 근접 무기를 휘둘러 적을 공격한다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MoveSpeed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DetectRange</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PatrolRange</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AttackRange</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PrefabPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PatrolSpeed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>몬스터를 우선 프리팹으로 구현</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AttackCoolTime</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mob_goblin_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>몬스터 설명 (도감용)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mob_goblin_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>몬스터 표기용 Icon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AttackDamage</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MaxHp</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>레드 고블린</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그린 고블린</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>float</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -247,7 +253,7 @@
     </x:xf>
   </x:cellStyleXfs>
   <x:cellXfs count="16">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -914,58 +920,58 @@
   <x:sheetData>
     <x:row r="1" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D1" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E1" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:13" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G2" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H2" s="3" t="s">
-        <x:v>26</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="I2" s="3" t="s">
-        <x:v>26</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="J2" s="3" t="s">
-        <x:v>26</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="K2" s="3" t="s">
-        <x:v>26</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="L2" s="3" t="s">
-        <x:v>26</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="M2" s="3" t="s">
-        <x:v>26</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:13" s="13" customFormat="1" ht="15.75" customHeight="1">
@@ -973,54 +979,56 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B3" s="12" t="s">
-        <x:v>24</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C3" s="12" t="s">
-        <x:v>8</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D3" s="14" t="s">
-        <x:v>9</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E3" s="14" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F3" s="14" t="s">
-        <x:v>20</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="G3" s="13" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="H3" s="13" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I3" s="13" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="H3" s="13" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="I3" s="13" t="s">
+      <x:c r="J3" s="13" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="K3" s="13" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="L3" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="J3" s="13" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="K3" s="13" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="L3" s="13" t="s">
-        <x:v>7</x:v>
-      </x:c>
       <x:c r="M3" s="13" t="s">
-        <x:v>13</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A4" s="4" t="s">
-        <x:v>14</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B4" s="4" t="s">
-        <x:v>23</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C4" s="4" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D4" s="5"/>
+      <x:c r="E4" s="5" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D4" s="5"/>
-      <x:c r="E4" s="5"/>
       <x:c r="F4" s="15">
         <x:v>10</x:v>
       </x:c>
@@ -1050,16 +1058,18 @@
     </x:row>
     <x:row r="5" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A5" s="4" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B5" s="6" t="s">
-        <x:v>22</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C5" s="6" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D5" s="5"/>
+      <x:c r="E5" s="5" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D5" s="5"/>
-      <x:c r="E5" s="5"/>
       <x:c r="F5" s="5">
         <x:v>30</x:v>
       </x:c>

--- a/JsonConverter/ExcelFiles/MGMonster.xlsx
+++ b/JsonConverter/ExcelFiles/MGMonster.xlsx
@@ -21,10 +21,10 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="29">
   <x:si>
-    <x:t>Prefab/2D/Monster</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefab/2D/Monster_Red</x:t>
+    <x:t>Prefabs/2D/Monster_Red</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/2D/Monster</x:t>
   </x:si>
   <x:si>
     <x:t>빨간색 고블린, 근접 무기를 휘둘러 적을 공격한다.</x:t>
@@ -1027,7 +1027,7 @@
       </x:c>
       <x:c r="D4" s="5"/>
       <x:c r="E4" s="5" t="s">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F4" s="15">
         <x:v>10</x:v>
@@ -1068,7 +1068,7 @@
       </x:c>
       <x:c r="D5" s="5"/>
       <x:c r="E5" s="5" t="s">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F5" s="5">
         <x:v>30</x:v>

--- a/JsonConverter/ExcelFiles/MGMonster.xlsx
+++ b/JsonConverter/ExcelFiles/MGMonster.xlsx
@@ -19,15 +19,54 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="29">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="35">
   <x:si>
     <x:t>Prefabs/2D/Monster_Red</x:t>
   </x:si>
   <x:si>
+    <x:t>녹색 고블린, 적을 보면 돌을 던진다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>빨간색 고블린, 근접 무기를 휘둘러 적을 공격한다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AttackDamage</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AttackCoolTime</x:t>
+  </x:si>
+  <x:si>
+    <x:t>몬스터 설명 (도감용)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mob_goblin_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>몬스터 표기용 Icon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mob_goblin_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>몬스터를 우선 프리팹으로 구현</x:t>
+  </x:si>
+  <x:si>
     <x:t>Prefabs/2D/Monster</x:t>
   </x:si>
   <x:si>
-    <x:t>빨간색 고블린, 근접 무기를 휘둘러 적을 공격한다.</x:t>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그린 고블린</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
   </x:si>
   <x:si>
     <x:t>레드 고블린</x:t>
@@ -36,76 +75,55 @@
     <x:t>MaxHp</x:t>
   </x:si>
   <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그린 고블린</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
+    <x:t>float</x:t>
   </x:si>
   <x:si>
     <x:t>(name)</x:t>
   </x:si>
   <x:si>
-    <x:t>float</x:t>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AttackRange</x:t>
   </x:si>
   <x:si>
     <x:t>PrefabPath</x:t>
   </x:si>
   <x:si>
-    <x:t>AttackRange</x:t>
+    <x:t>DetectRange</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MoveSpeed</x:t>
   </x:si>
   <x:si>
     <x:t>PatrolRange</x:t>
   </x:si>
   <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DetectRange</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MoveSpeed</x:t>
-  </x:si>
-  <x:si>
     <x:t>PatrolSpeed</x:t>
   </x:si>
   <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>몬스터를 우선 프리팹으로 구현</x:t>
-  </x:si>
-  <x:si>
-    <x:t>몬스터 표기용 Icon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mob_goblin_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>몬스터 설명 (도감용)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AttackDamage</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mob_goblin_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AttackCoolTime</x:t>
-  </x:si>
-  <x:si>
-    <x:t>녹색 고블린, 적을 보면 돌을 던진다.</x:t>
+    <x:t>Prefabs/2D/Projectile_GoblinStone</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AttackType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Melee</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ranged</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ProjectileSpeed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ProjectilePrefabPath</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -905,7 +923,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:O35"/>
+  <x:dimension ref="A1:R35"/>
   <x:sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15" customHeight="1"/>
   <x:cols>
     <x:col min="1" max="1" width="19.453125" style="3" customWidth="1"/>
@@ -914,120 +932,138 @@
     <x:col min="4" max="4" width="20.26953125" style="3" customWidth="1"/>
     <x:col min="5" max="5" width="30.54296875" style="3" customWidth="1"/>
     <x:col min="6" max="6" width="26.54296875" style="3" customWidth="1"/>
-    <x:col min="7" max="13" width="20.71484375" style="3" customWidth="1"/>
-    <x:col min="14" max="16384" width="12.54296875" style="3"/>
+    <x:col min="7" max="16" width="20.71484375" style="3" customWidth="1"/>
+    <x:col min="17" max="16384" width="12.54296875" style="3"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D1" s="2" t="s">
-        <x:v>22</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E1" s="2" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:13" ht="13.199999999999999">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:16" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G2" s="3" t="s">
-        <x:v>20</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="H2" s="3" t="s">
-        <x:v>9</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="I2" s="3" t="s">
-        <x:v>9</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="J2" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="K2" s="3" t="s">
-        <x:v>9</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="L2" s="3" t="s">
-        <x:v>9</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="M2" s="3" t="s">
-        <x:v>9</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:13" s="13" customFormat="1" ht="15.75" customHeight="1">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="N2" s="3" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="O2" s="3" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="P2" s="3" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:16" s="13" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B3" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C3" s="12" t="s">
-        <x:v>13</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D3" s="14" t="s">
-        <x:v>14</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E3" s="14" t="s">
-        <x:v>10</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F3" s="14" t="s">
-        <x:v>4</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G3" s="13" t="s">
-        <x:v>25</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H3" s="13" t="s">
-        <x:v>17</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="I3" s="13" t="s">
-        <x:v>18</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="J3" s="13" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="K3" s="13" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="L3" s="13" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="M3" s="13" t="s">
         <x:v>27</x:v>
       </x:c>
-    </x:row>
-    <x:row r="4" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="N3" s="13" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="O3" s="13" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="P3" s="13" t="s">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A4" s="4" t="s">
-        <x:v>23</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B4" s="4" t="s">
-        <x:v>6</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C4" s="4" t="s">
-        <x:v>28</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D4" s="5"/>
       <x:c r="E4" s="5" t="s">
-        <x:v>1</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F4" s="15">
         <x:v>10</x:v>
@@ -1035,33 +1071,42 @@
       <x:c r="G4" s="5">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="H4" s="5">
+      <x:c r="H4" s="5" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="I4" s="5" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="J4" s="5">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K4" s="5">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="I4" s="5">
+      <x:c r="L4" s="5">
         <x:v>1.5</x:v>
       </x:c>
-      <x:c r="J4" s="5">
+      <x:c r="M4" s="5">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K4" s="5">
+      <x:c r="N4" s="5">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="L4" s="5">
+      <x:c r="O4" s="5">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="M4" s="5">
+      <x:c r="P4" s="5">
         <x:v>1.5</x:v>
       </x:c>
-      <x:c r="N4" s="5"/>
-      <x:c r="O4" s="5"/>
-    </x:row>
-    <x:row r="5" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="Q4" s="5"/>
+      <x:c r="R4" s="5"/>
+    </x:row>
+    <x:row r="5" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A5" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B5" s="6" t="s">
-        <x:v>3</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C5" s="6" t="s">
         <x:v>2</x:v>
@@ -1076,28 +1121,35 @@
       <x:c r="G5" s="5">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="H5" s="5">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="I5" s="5">
-        <x:v>1.5</x:v>
-      </x:c>
+      <x:c r="H5" s="5" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="I5" s="5"/>
       <x:c r="J5" s="5">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K5" s="5">
         <x:v>3</x:v>
       </x:c>
       <x:c r="L5" s="5">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="M5" s="5">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="N5" s="5">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O5" s="5">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="M5" s="5">
+      <x:c r="P5" s="5">
         <x:v>1.5</x:v>
       </x:c>
-      <x:c r="N5" s="5"/>
-      <x:c r="O5" s="5"/>
-    </x:row>
-    <x:row r="6" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="Q5" s="5"/>
+      <x:c r="R5" s="5"/>
+    </x:row>
+    <x:row r="6" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A6" s="6"/>
       <x:c r="B6" s="6"/>
       <x:c r="C6" s="6"/>
@@ -1113,8 +1165,11 @@
       <x:c r="M6" s="5"/>
       <x:c r="N6" s="5"/>
       <x:c r="O6" s="5"/>
-    </x:row>
-    <x:row r="7" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="P6" s="5"/>
+      <x:c r="Q6" s="5"/>
+      <x:c r="R6" s="5"/>
+    </x:row>
+    <x:row r="7" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A7" s="4"/>
       <x:c r="B7" s="4"/>
       <x:c r="C7" s="4"/>
@@ -1130,8 +1185,11 @@
       <x:c r="M7" s="5"/>
       <x:c r="N7" s="5"/>
       <x:c r="O7" s="5"/>
-    </x:row>
-    <x:row r="8" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="P7" s="5"/>
+      <x:c r="Q7" s="5"/>
+      <x:c r="R7" s="5"/>
+    </x:row>
+    <x:row r="8" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A8" s="7"/>
       <x:c r="B8" s="7"/>
       <x:c r="C8" s="7"/>
@@ -1147,8 +1205,11 @@
       <x:c r="M8" s="5"/>
       <x:c r="N8" s="5"/>
       <x:c r="O8" s="5"/>
-    </x:row>
-    <x:row r="9" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="P8" s="5"/>
+      <x:c r="Q8" s="5"/>
+      <x:c r="R8" s="5"/>
+    </x:row>
+    <x:row r="9" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A9" s="7"/>
       <x:c r="B9" s="7"/>
       <x:c r="C9" s="7"/>
@@ -1164,8 +1225,11 @@
       <x:c r="M9" s="5"/>
       <x:c r="N9" s="5"/>
       <x:c r="O9" s="5"/>
-    </x:row>
-    <x:row r="10" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="P9" s="5"/>
+      <x:c r="Q9" s="5"/>
+      <x:c r="R9" s="5"/>
+    </x:row>
+    <x:row r="10" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A10" s="1"/>
       <x:c r="B10" s="1"/>
       <x:c r="C10" s="1"/>
@@ -1181,8 +1245,11 @@
       <x:c r="M10" s="5"/>
       <x:c r="N10" s="5"/>
       <x:c r="O10" s="5"/>
-    </x:row>
-    <x:row r="11" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="P10" s="5"/>
+      <x:c r="Q10" s="5"/>
+      <x:c r="R10" s="5"/>
+    </x:row>
+    <x:row r="11" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A11" s="1"/>
       <x:c r="B11" s="1"/>
       <x:c r="C11" s="1"/>
@@ -1198,8 +1265,11 @@
       <x:c r="M11" s="5"/>
       <x:c r="N11" s="5"/>
       <x:c r="O11" s="5"/>
-    </x:row>
-    <x:row r="12" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="P11" s="5"/>
+      <x:c r="Q11" s="5"/>
+      <x:c r="R11" s="5"/>
+    </x:row>
+    <x:row r="12" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A12" s="7"/>
       <x:c r="B12" s="7"/>
       <x:c r="C12" s="7"/>
@@ -1215,8 +1285,11 @@
       <x:c r="M12" s="5"/>
       <x:c r="N12" s="5"/>
       <x:c r="O12" s="5"/>
-    </x:row>
-    <x:row r="13" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="P12" s="5"/>
+      <x:c r="Q12" s="5"/>
+      <x:c r="R12" s="5"/>
+    </x:row>
+    <x:row r="13" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A13" s="4"/>
       <x:c r="B13" s="4"/>
       <x:c r="C13" s="4"/>
@@ -1232,8 +1305,11 @@
       <x:c r="M13" s="5"/>
       <x:c r="N13" s="5"/>
       <x:c r="O13" s="5"/>
-    </x:row>
-    <x:row r="14" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="P13" s="5"/>
+      <x:c r="Q13" s="5"/>
+      <x:c r="R13" s="5"/>
+    </x:row>
+    <x:row r="14" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A14" s="1"/>
       <x:c r="B14" s="1"/>
       <x:c r="C14" s="1"/>
@@ -1249,8 +1325,11 @@
       <x:c r="M14" s="5"/>
       <x:c r="N14" s="5"/>
       <x:c r="O14" s="5"/>
-    </x:row>
-    <x:row r="15" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="P14" s="5"/>
+      <x:c r="Q14" s="5"/>
+      <x:c r="R14" s="5"/>
+    </x:row>
+    <x:row r="15" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A15" s="1"/>
       <x:c r="B15" s="1"/>
       <x:c r="C15" s="1"/>
@@ -1266,6 +1345,9 @@
       <x:c r="M15" s="5"/>
       <x:c r="N15" s="5"/>
       <x:c r="O15" s="5"/>
+      <x:c r="P15" s="5"/>
+      <x:c r="Q15" s="5"/>
+      <x:c r="R15" s="5"/>
     </x:row>
     <x:row r="16" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A16" s="8"/>

--- a/JsonConverter/ExcelFiles/MGMonster.xlsx
+++ b/JsonConverter/ExcelFiles/MGMonster.xlsx
@@ -21,109 +21,109 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="35">
   <x:si>
+    <x:t>Prefabs/2D/Projectile_GoblinStone</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/2D/Monster</x:t>
+  </x:si>
+  <x:si>
+    <x:t>몬스터를 우선 프리팹으로 구현</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AttackCoolTime</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AttackDamage</x:t>
+  </x:si>
+  <x:si>
+    <x:t>몬스터 설명 (도감용)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mob_goblin_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mob_goblin_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ProjectileSpeed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>몬스터 표기용 Icon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>빨간색 고블린, 근접 무기를 휘둘러 적을 공격한다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AttackRange</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PatrolSpeed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DetectRange</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PatrolRange</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MoveSpeed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PrefabPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AttackType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그린 고블린</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>레드 고블린</x:t>
+  </x:si>
+  <x:si>
+    <x:t>float</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MaxHp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Melee</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ranged</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ProjectilePrefabPath</x:t>
+  </x:si>
+  <x:si>
     <x:t>Prefabs/2D/Monster_Red</x:t>
   </x:si>
   <x:si>
     <x:t>녹색 고블린, 적을 보면 돌을 던진다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>빨간색 고블린, 근접 무기를 휘둘러 적을 공격한다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AttackDamage</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AttackCoolTime</x:t>
-  </x:si>
-  <x:si>
-    <x:t>몬스터 설명 (도감용)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mob_goblin_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>몬스터 표기용 Icon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mob_goblin_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>몬스터를 우선 프리팹으로 구현</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/2D/Monster</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그린 고블린</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>레드 고블린</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MaxHp</x:t>
-  </x:si>
-  <x:si>
-    <x:t>float</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AttackRange</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PrefabPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DetectRange</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MoveSpeed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PatrolRange</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PatrolSpeed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/2D/Projectile_GoblinStone</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AttackType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Melee</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ranged</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ProjectileSpeed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ProjectilePrefabPath</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -938,132 +938,132 @@
   <x:sheetData>
     <x:row r="1" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1" t="s">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D1" s="2" t="s">
-        <x:v>7</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E1" s="2" t="s">
-        <x:v>11</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:16" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G2" s="3" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H2" s="3" t="s">
-        <x:v>13</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="I2" s="3" t="s">
-        <x:v>13</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="J2" s="3" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="K2" s="3" t="s">
-        <x:v>18</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="L2" s="3" t="s">
-        <x:v>18</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="M2" s="3" t="s">
-        <x:v>18</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="N2" s="3" t="s">
-        <x:v>18</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="O2" s="3" t="s">
-        <x:v>18</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="P2" s="3" t="s">
-        <x:v>18</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:16" s="13" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="12" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B3" s="12" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D3" s="14" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E3" s="14" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F3" s="14" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="G3" s="13" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H3" s="13" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="I3" s="13" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="J3" s="13" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K3" s="13" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="L3" s="13" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="M3" s="13" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="N3" s="13" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="O3" s="13" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C3" s="12" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="D3" s="14" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="E3" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="F3" s="14" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G3" s="13" t="s">
+      <x:c r="P3" s="13" t="s">
         <x:v>3</x:v>
-      </x:c>
-      <x:c r="H3" s="13" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="I3" s="13" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="J3" s="13" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="K3" s="13" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="L3" s="13" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="M3" s="13" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="N3" s="13" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="O3" s="13" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="P3" s="13" t="s">
-        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A4" s="4" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B4" s="4" t="s">
-        <x:v>14</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C4" s="4" t="s">
-        <x:v>1</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D4" s="5"/>
       <x:c r="E4" s="5" t="s">
-        <x:v>12</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F4" s="15">
         <x:v>10</x:v>
@@ -1072,10 +1072,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="H4" s="5" t="s">
-        <x:v>32</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="I4" s="5" t="s">
-        <x:v>29</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J4" s="5">
         <x:v>6</x:v>
@@ -1090,10 +1090,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="N4" s="5">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="O4" s="5">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="P4" s="5">
         <x:v>1.5</x:v>
@@ -1103,17 +1103,17 @@
     </x:row>
     <x:row r="5" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A5" s="4" t="s">
-        <x:v>8</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B5" s="6" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C5" s="6" t="s">
-        <x:v>2</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D5" s="5"/>
       <x:c r="E5" s="5" t="s">
-        <x:v>0</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F5" s="5">
         <x:v>30</x:v>
@@ -1122,7 +1122,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="H5" s="5" t="s">
-        <x:v>31</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="I5" s="5"/>
       <x:c r="J5" s="5">
